--- a/Longitudinal/LORA/CODEBOOK_LORA.xlsx
+++ b/Longitudinal/LORA/CODEBOOK_LORA.xlsx
@@ -42833,7 +42833,7 @@
     <mergeCell ref="I1461:I1467"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="H604" r:id="rId2" display="DeepL.com"/>
+    <hyperlink ref="H604" r:id="rId2" display="The total value is calculated by adding up all items:&#10;CERQ_total_1.0=cerq_1.0_1 + cerq_1.0_2 + cerq_1.0_3 + cerq_1.0_4 + cerq_1.0_5 + cerq_1.0_6 + cerq_1. 0_7 + cerq_1.0_8 + cerq_1.0_9 + cerq_1.0_10 + cerq_1.0_11 + cerq_1.0_12 + cerq_1.0_13 + cerq_1.0_14 + cerq_1. 0_15 + cerq_1.0_16 + cerq_1.0_17 + cerq_1.0_18 + cerq_1.0_19 + cerq_1.0_20 + cerq_1.0_21 + cerq_1.0_22 + cerq_1.0_23 + cerq_1.0_24 + cerq_1.0_25 + cerq_1.0_26 + cerq_1.0_27 + cerq_1.0_28 + cerq_1.0_29.&#10;&#10;The individual scales are calculated by adding up the respective items:&#10;CERQ_SeBes_1.0=cerq_1.0_1 + cerq_1.0_10 + cerq_1.0_19.&#10;&#10;CERQ_Akzep_1.0=cerq_1.0_2 + cerq_1.0_11 + cerq_1.0_20.&#10;&#10;CERQ_Rumi_1.0=cerq_1.0_3 + cerq_1.0_12 + cerq_1.0_21.&#10;&#10;CERQ_PoRef_1.0=cerq_1.0_4 + cerq_1.0_13 + cerq_1.0_22.&#10;&#10;CERQ_Plan_1.0=cerq_1.0_5 + cerq_1.0_14 + cerq_1.0_23.&#10;&#10;CERQ_PoNeu_1.0=cerq_1.0_6 + cerq_1.0_15 + cerq_1.0_24.&#10;&#10;CERQ_Relat_1.0=cerq_1.0_7 + cerq_1.0_16 + cerq_1.0_25.&#10;&#10;CERQ_Katast_1.0=cerq_1.0_8 + cerq_1.0_17 + cerq_1.0_26.&#10;&#10;CERQ_AnBes_1.0=cerq_1.0_9 + cerq_1.0_18 + cerq_1.0_27.&#10;&#10;CERQ_KoDist_1.0=cerq_1.0_28 + cerq_1.0_29.&#10;&#10;From this, adaptive and maladaptive (functional and dysfunctional) scores can be calculated:&#10;adaptive:&#10;CERQ_malad_1.0=CERQ_AnBes_1.0 + CERQ_Katast_1.0 + CERQ_Rumi_1.0 + CERQ_SeBes_1.0.&#10;&#10;maladaptive:&#10;CERQ_adap_1.0= CERQ_Relat_1.0 + CERQ_PoNeu_1.0 + CERQ_Plan_1.0 + CERQ_PoRef_1.0 + CERQ_Akzep_1.0.&#10;Translated with DeepL.com (free version)&#10;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
